--- a/docs/gebruikershandleiding/publiceren/woo-besluit/productierapport_template.xlsx
+++ b/docs/gebruikershandleiding/publiceren/woo-besluit/productierapport_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Paul/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Shared/Storage/Repos/minvws/nl-rdo-woo-web-private/docs/gebruikershandleiding/publiceren/woo-besluit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A919043-F424-E340-99F2-C6E6DAE9F4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5C053D-203A-9F44-A4C3-CFA5EE45CCF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33100" yWindow="4020" windowWidth="41540" windowHeight="13980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45720" yWindow="1960" windowWidth="41540" windowHeight="13980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -217,7 +217,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -228,9 +228,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent2" xfId="1" builtinId="33"/>
@@ -311,8 +308,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0D08D747-B30F-E34B-AF0C-335900D11E1A}" name="Beoordeling" displayName="Beoordeling" ref="B2:B7" totalsRowShown="0">
-  <autoFilter ref="B2:B7" xr:uid="{0D08D747-B30F-E34B-AF0C-335900D11E1A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0D08D747-B30F-E34B-AF0C-335900D11E1A}" name="Beoordeling" displayName="Beoordeling" ref="B2:B6" totalsRowShown="0">
+  <autoFilter ref="B2:B6" xr:uid="{0D08D747-B30F-E34B-AF0C-335900D11E1A}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{12A7CDB3-6A20-B142-BB21-05AFF9334A6D}" name="Beoordeling"/>
   </tableColumns>
@@ -752,7 +749,7 @@
       <c r="H3" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="6"/>
+      <c r="I3" s="2"/>
       <c r="M3" s="2">
         <v>10001</v>
       </c>
@@ -842,7 +839,7 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Het type bronbestand. Mogelijke types zijn: pdf, doc, image, presentation, spreadsheet, email, html, note, database, xml, video, audio, vcard, chat." xr:uid="{0B13E08D-B13E-DD4A-B934-3527E09D582A}">
           <x14:formula1>
             <xm:f>'Lookup values'!$F$3:$F$16</xm:f>
@@ -854,6 +851,12 @@
             <xm:f>'Lookup values'!$D$3:$D$4</xm:f>
           </x14:formula1>
           <xm:sqref>I2 I4:I5</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F3B1EB8D-A497-4B48-B7C8-CA3256E9196F}">
+          <x14:formula1>
+            <xm:f>'Lookup values'!$B$3:$B$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>H2:H5</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
